--- a/Config/Datas/cult_tech.xlsx
+++ b/Config/Datas/cult_tech.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cult_tech_node" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cult_tech_node_level" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cult_tech_node" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="cult_tech_node_level" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -764,7 +764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +798,16 @@
           <t>effect_desc</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>cult_attr</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>cult_attr_value</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -830,6 +840,16 @@
           <t>string</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -862,6 +882,16 @@
           <t>c,s</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -894,6 +924,16 @@
           <t>效果说明(占位)</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>教团属性</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>教团属性值</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -909,6 +949,9 @@
         <is>
           <t>解锁教团布道树外环。</t>
         </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -931,6 +974,14 @@
           <t>解锁暗室密传相关占位效果。</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TownDailyFaith</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
@@ -952,6 +1003,9 @@
           <t>解锁梦中显圣相关占位效果。</t>
         </is>
       </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
@@ -973,6 +1027,9 @@
           <t>解锁威压改宗相关占位效果。</t>
         </is>
       </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
@@ -994,6 +1051,9 @@
           <t>解锁工艺贡礼相关占位效果。</t>
         </is>
       </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
@@ -1010,6 +1070,9 @@
           <t>淑女残座共鸣：往去回忆事件占位。</t>
         </is>
       </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
@@ -1030,6 +1093,321 @@
         <is>
           <t>血契布道效率占位提升。</t>
         </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>22</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>25</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>残页誓词占位效果。</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>23</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>25</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>梦痕收集占位效果。</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>24</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>30</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>夜半宣讲占位效果。</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>25</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>35</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>无名灯塔占位效果。</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>26</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>25</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>惊惧刻印占位效果。</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>27</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>30</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>沉默注视占位效果。</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>28</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>35</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>服从仪式占位效果。</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>29</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>25</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>献礼熔炉占位效果。</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>30</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>30</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>丝线圣痕占位效果。</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>31</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>35</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>宴席余香占位效果。</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>32</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>25</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>秘仪徽章占位效果。</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>33</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>30</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>温柔陷阱占位效果。</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>34</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>35</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>回声工坊占位效果。</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/cult_tech.xlsx
+++ b/Config/Datas/cult_tech.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,7 +596,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>教团权能的核心。铭刻后可向外延展布道戒律。</t>
+          <t>教团权能的核心。铭刻后可向外延展布道戒律，并获得初始秘会席位。</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -615,12 +615,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>暗室密传</t>
+          <t>灵感回响</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>以隐秘方式传播教义，侧重亵渎材料与低暴露。</t>
+          <t>各地偶有人突发灵感皈依。各地区每日自然增加教徒。</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -639,12 +639,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>梦中显圣</t>
+          <t>秘会编制</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>借梦境显圣传教，与入梦玩法呼应。</t>
+          <t>编制更多可调度的秘会席位，用于耗时布道事务。</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -663,12 +663,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>威压改宗</t>
+          <t>低语什一</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>以威压迫使改宗，信仰来得快，人间关系风险高。</t>
+          <t>教徒以低语供奉信仰。按总教徒日产微量信仰，不能替代锚点主矿。</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>工艺贡礼</t>
+          <t>圣地回馈</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>以精致工艺品为贡礼传教，衔接文明副产物献纳。</t>
+          <t>已建立的锚点按稀有度在周期结算时额外产出信仰。</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -711,12 +711,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>往去余韵</t>
+          <t>教团洞见</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>供奉「淑女」残座的入门铭刻，可触发往去回忆碎片。</t>
+          <t>洞悉教团隐秘线索。解锁高级教团情报的出现条件。</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -735,12 +735,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>血契布道</t>
+          <t>灵感回响·贰</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>将密传与血契结合，提升传教效率（占位效果）。</t>
+          <t>灵感共鸣加深。各地区每日再增加教徒。</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -751,6 +751,78 @@
       </c>
       <c r="G12" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>22</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>城镇残晖</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>受控城镇日结上缴微量信仰。</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>23</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>圣地回馈·贰</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>圣地回馈加深。锚点稀有度额外信仰再提升。</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>24</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>远征补给</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>完善外派补给规程。远征出征点的基础产出提高10%。</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -764,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -921,7 +993,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>效果说明(占位)</t>
+          <t>效果说明</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -947,11 +1019,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>解锁教团布道树外环。</t>
+          <t>解锁教团布道树，获得 1 个秘会席位。</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SecretUnitSlot</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -971,12 +1048,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>解锁暗室密传相关占位效果。</t>
+          <t>各地区每日自然皈依 +1 教徒。</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>TownDailyFaith</t>
+          <t>RegionDailyLinker</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1000,11 +1077,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>解锁梦中显圣相关占位效果。</t>
+          <t>额外解锁 1 个秘会席位。</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SecretUnitSlot</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1024,11 +1106,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>解锁威压改宗相关占位效果。</t>
+          <t>每日信仰 += 总教徒 × 本值 / 100。</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>LinkerFaithRate</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1048,11 +1135,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>解锁工艺贡礼相关占位效果。</t>
+          <t>锚点周期额外信仰 += 稀有度 × 本值。</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>AnchorRarityFaithBonus</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1062,12 +1154,17 @@
       <c r="C11" t="n">
         <v>1</v>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="E11" t="n">
         <v>80</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>淑女残座共鸣：往去回忆事件占位。</t>
+          <t>解锁高级教团情报（CommonCond: CultTechNodeLevel）。</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1091,11 +1188,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>血契布道效率占位提升。</t>
+          <t>各地区每日自然皈依再 +1 教徒。</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>RegionDailyLinker</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1115,11 +1217,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>残页誓词占位效果。</t>
+          <t>每个受控城镇日结信仰 +1。</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>TownDailyFaith</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1131,19 +1238,24 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>梦痕收集占位效果。</t>
+          <t>锚点周期额外信仰再 +稀有度 × 1。</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>AnchorRarityFaithBonus</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1159,255 +1271,20 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>夜半宣讲占位效果。</t>
+          <t>远征基础产出 +10%。</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ScoutLootBonusPercent</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="n">
-        <v>25</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>35</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>无名灯塔占位效果。</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="n">
-        <v>26</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>25</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>惊惧刻印占位效果。</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="n">
-        <v>27</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>30</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>沉默注视占位效果。</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="n">
-        <v>28</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>35</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>服从仪式占位效果。</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="n">
-        <v>29</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>25</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>献礼熔炉占位效果。</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="n">
-        <v>30</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>30</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>丝线圣痕占位效果。</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" t="n">
-        <v>31</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>35</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>宴席余香占位效果。</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="n">
-        <v>32</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>25</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>秘仪徽章占位效果。</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="n">
-        <v>33</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>30</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>温柔陷阱占位效果。</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="n">
-        <v>34</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>35</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>回声工坊占位效果。</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
